--- a/Data penjualan karim Gadget.xlsx
+++ b/Data penjualan karim Gadget.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Coding\Laporan Keuangan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Coding\Laporan Keuangan - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084FBAC2-9021-4907-A987-B034066C3116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEDDA4BB-876F-4700-93AB-FF967C5857A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Real Time" sheetId="1" r:id="rId1"/>
@@ -444,6 +444,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -451,9 +454,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -2210,7 +2210,7 @@
       <c r="A58">
         <v>57</v>
       </c>
-      <c r="B58" s="75">
+      <c r="B58" s="72">
         <v>46238</v>
       </c>
       <c r="C58" s="29">
@@ -2234,7 +2234,7 @@
       <c r="A59" s="69">
         <v>58</v>
       </c>
-      <c r="B59" s="75">
+      <c r="B59" s="72">
         <v>46260</v>
       </c>
       <c r="C59" s="62">
@@ -2249,7 +2249,7 @@
       <c r="F59" s="67">
         <v>7800000</v>
       </c>
-      <c r="G59" s="74">
+      <c r="G59" s="71">
         <f>SUM(F59-E59)</f>
         <v>402500</v>
       </c>
@@ -2259,7 +2259,7 @@
       <c r="A60" s="69">
         <v>59</v>
       </c>
-      <c r="B60" s="75">
+      <c r="B60" s="72">
         <v>46260</v>
       </c>
       <c r="C60" s="69"/>
@@ -2282,7 +2282,7 @@
       <c r="D61" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="E61" s="73">
+      <c r="E61" s="70">
         <v>12900000</v>
       </c>
       <c r="G61" s="17"/>
@@ -2642,14 +2642,14 @@
       <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
       <c r="G4" s="57">
         <f>SUM(G2+G3)</f>
         <v>1000000</v>
@@ -2906,14 +2906,14 @@
       <c r="H9" s="17"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
       <c r="G10" s="56">
         <f>SUM(G2+G3+G4+G5+G6+G7+G9)</f>
         <v>3525000</v>
@@ -3060,14 +3060,14 @@
       <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="70" t="s">
+      <c r="A4" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="71"/>
-      <c r="C4" s="71"/>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71"/>
-      <c r="F4" s="71"/>
+      <c r="B4" s="74"/>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
       <c r="G4" s="57">
         <f>SUM(G2+G3)</f>
         <v>1100000</v>
@@ -3272,14 +3272,14 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
       <c r="G8" s="57">
         <f>SUM(G2:G7)</f>
         <v>3750000</v>
@@ -3412,12 +3412,12 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="72" t="s">
+      <c r="A5" s="75" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
+      <c r="B5" s="75"/>
+      <c r="C5" s="75"/>
+      <c r="D5" s="75"/>
       <c r="E5" s="32"/>
       <c r="F5" s="32"/>
       <c r="G5" s="64">
@@ -3541,7 +3541,7 @@
         <v>46238</v>
       </c>
       <c r="C2" s="29">
-        <v>44078</v>
+        <v>46269</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>31</v>
@@ -3652,7 +3652,7 @@
       <c r="D2" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="73">
+      <c r="E2" s="70">
         <v>12900000</v>
       </c>
       <c r="F2" s="63"/>
@@ -4299,14 +4299,14 @@
       <c r="H24" s="17"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="70" t="s">
+      <c r="A25" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="71"/>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="71"/>
-      <c r="F25" s="71"/>
+      <c r="B25" s="74"/>
+      <c r="C25" s="74"/>
+      <c r="D25" s="74"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
       <c r="G25" s="57">
         <f>SUM(G2:G24)</f>
         <v>8036505</v>
@@ -4460,14 +4460,14 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="57">
         <f>SUM(G2:G5)</f>
         <v>930000</v>
@@ -4748,14 +4748,14 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="70" t="s">
+      <c r="A10" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="71"/>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="71"/>
-      <c r="F10" s="71"/>
+      <c r="B10" s="74"/>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
       <c r="G10" s="57">
         <f>SUM(G2:G9)</f>
         <v>2781505</v>
@@ -4910,14 +4910,14 @@
       <c r="H5" s="17"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="71"/>
-      <c r="C6" s="71"/>
-      <c r="D6" s="71"/>
-      <c r="E6" s="71"/>
-      <c r="F6" s="71"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
       <c r="G6" s="57">
         <f>SUM(G2:G5)</f>
         <v>1500000</v>
@@ -5147,14 +5147,14 @@
       <c r="H8" s="17"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="70" t="s">
+      <c r="A9" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B9" s="71"/>
-      <c r="C9" s="71"/>
-      <c r="D9" s="71"/>
-      <c r="E9" s="71"/>
-      <c r="F9" s="71"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="74"/>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
       <c r="G9" s="57">
         <f>SUM(G2:G8)</f>
         <v>2825000</v>
@@ -6263,14 +6263,14 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
       <c r="G8" s="57">
         <f>SUM(G2+G3+G4+G5+G6+G7)</f>
         <v>1730000</v>
@@ -6476,14 +6476,14 @@
       <c r="H7" s="17"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="71"/>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="71"/>
-      <c r="F8" s="71"/>
+      <c r="B8" s="74"/>
+      <c r="C8" s="74"/>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
       <c r="G8" s="57">
         <f>SUM(G2+G3+G4+G5+G6+G7)</f>
         <v>1936875</v>
